--- a/hyd_realestate_2026-05-09.xlsx
+++ b/hyd_realestate_2026-05-09.xlsx
@@ -15,12 +15,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="USER PROFILES" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'LEADS'!$A$1:$T$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'FLATS'!$A$1:$L$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'LEADS'!$A$1:$T$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'FLATS'!$A$1:$L$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'VILLAS'!$A$1:$L$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'PLOTS'!$A$1:$L$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'OTHERS'!$A$1:$L$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'USER PROFILES'!$A$1:$S$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'USER PROFILES'!$A$1:$S$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T11"/>
+  <dimension ref="A1:T10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>14.3</v>
+        <v>15.1</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Author explicitly looking to buy a gated villa in a specific area with a clear budget.</t>
+          <t>Author explicitly states they are looking to buy a gated villa with a clear budget and location.</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr"/>
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>11</v>
+        <v>11.8</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Tukkuguda/Mokila</t>
+          <t>Tukkuguda/Mokila/Shankarpally</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Author explicitly looking to buy a villa with a clear budget, locations, and timeline.</t>
+          <t>Author has clear buying intent for a villa with defined budget, multiple shortlisted locations, and timeline for appreciation.</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr"/>
@@ -774,7 +774,7 @@
         <v>20</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="S3" s="3" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>8</v>
@@ -816,7 +816,7 @@
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>EIPL Cornerstone / The Drizzle by Ananda Homes</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Author is actively searching for a 3BHK end-use unit in two named projects with clear preferences.</t>
+          <t>Author is actively searching for a 3BHK in two specific projects for end use and requesting unit availability.</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr"/>
@@ -855,7 +855,7 @@
         <v>2</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R4" s="2" t="n">
         <v>100</v>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>15.5</v>
+        <v>16.3</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Author explicitly states need to buy a 3BHK flat in a specific project and shares contact number.</t>
+          <t>Author explicitly states intent to buy a specific 3BHK flat in a named project and shares contact details.</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr"/>
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Author is actively searching for plots or flats to buy in Hyderabad with a stated budget.</t>
+          <t>Author is actively searching for plots or flats to buy in Hyderabad with a clear budget.</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr"/>
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
       <c r="H7" s="2" t="inlineStr"/>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Nagaram, Maheshwaram (near Mansanpally)</t>
+          <t>Nagaram, Maheshwaram (near Mansanpally/ORR)</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Author is actively evaluating a specific plot purchase and seeking expert input on the location.</t>
+          <t>Author is evaluating a specific plot purchase and seeking expert input on location value.</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1117,11 +1117,11 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08 01:16</t>
+          <t>2026-05-08 01:38</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>23.4</v>
+        <v>23.8</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -1130,11 +1130,11 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>end_user</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>7</v>
@@ -1147,7 +1147,7 @@
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Jayabheri Nirvana</t>
+          <t>LB Nagar</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1157,37 +1157,37 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Author is actively buying a flat in a specific project and seeking pros/cons input.</t>
+          <t>Author explicitly wants to buy a flat in LB Nagar in a gated community and is evaluating Vasavi Ananda Nilayam.</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Jayabheri Nirvana</t>
+          <t>Vasavi ananda nilayam</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Buying a flat in jayabheri nirvana. Give me the pros and cons please. The major con I think of is the traffic near the market.</t>
+          <t xml:space="preserve">How's Vasavi ananda nilayam I want to buy a flat in LB Nagar area in a good  gated communitie, but heard so much  negative reviews about this project and Vasavi like project is delayed and work process is slow </t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>u/stoopidpotato_</t>
+          <t>u/Fun_Device_1371</t>
         </is>
       </c>
       <c r="P8" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>https://reddit.com/r/hyderabadrealestate/comments/1t6laei/jayabheri_nirvana/</t>
+          <t>https://reddit.com/r/hyderabadrealestate/comments/1t6lwft/vasavi_ananda_nilayam/</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr"/>
@@ -1195,11 +1195,11 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08 01:38</t>
+          <t>2026-05-08 15:43</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>23</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -1208,14 +1208,14 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>end_user</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
@@ -1223,11 +1223,7 @@
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>LB Nagar</t>
-        </is>
-      </c>
+      <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
           <t>flat</t>
@@ -1235,37 +1231,37 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Author explicitly wants to buy a flat in LB Nagar gated community and is evaluating Vasavi Ananda Nilayam.</t>
+          <t>Author is actively researching a specific project for purchase and checking booking status before committing.</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Vasavi ananda nilayam</t>
+          <t>Did anyone book a flat in Vaishno Sapphire?</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">How's Vasavi ananda nilayam I want to buy a flat in LB Nagar area in a good  gated communitie, but heard so much  negative reviews about this project and Vasavi like project is delayed and work process is slow </t>
+          <t xml:space="preserve">Hi, I was looking at Vaishno Sapphire project and noticed that there are 0 bookings listed on the RERA website. Will there be any delay in updating it or are there zero bookings really? But for the other projects, I am seeing some bookings on the RERA website. </t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>u/Fun_Device_1371</t>
+          <t>u/proton49</t>
         </is>
       </c>
       <c r="P9" s="2" t="n">
         <v>3</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R9" s="2" t="n">
         <v>100</v>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>https://reddit.com/r/hyderabadrealestate/comments/1t6lwft/vasavi_ananda_nilayam/</t>
+          <t>https://reddit.com/r/hyderabadrealestate/comments/1t73o7f/did_anyone_book_a_flat_in_vaishno_sapphire/</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr"/>
@@ -1273,11 +1269,11 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08 15:43</t>
+          <t>2026-05-08 19:45</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>9</v>
+        <v>5.7</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -1286,14 +1282,14 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>end_user</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
@@ -1301,131 +1297,53 @@
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>Vaishno Sapphire</t>
-        </is>
-      </c>
+      <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>flat</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Author is actively researching a specific project and checking booking status, indicating buying intent.</t>
+          <t>Author is actively searching for bank auction properties to purchase and seeking trusted sources.</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Did anyone book a flat in Vaishno Sapphire?</t>
+          <t>I need trusted websites to search for bank auction properties how's this https://bankauctiondeals.com/</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hi, I was looking at Vaishno Sapphire project and noticed that there are 0 bookings listed on the RERA website. Will there be any delay in updating it or are there zero bookings really? But for the other projects, I am seeing some bookings on the RERA website. </t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>u/proton49</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q10" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="S10" s="3" t="inlineStr">
-        <is>
-          <t>https://reddit.com/r/hyderabadrealestate/comments/1t73o7f/did_anyone_book_a_flat_in_vaishno_sapphire/</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-08 19:45</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>hyderabadrealestate</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>unclear</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>buying</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>unclear</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>Author is actively searching for bank auction properties to buy and seeking trusted resources.</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>I need trusted websites to search for bank auction properties how's this https://bankauctiondeals.com/</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">recently searched through this site 
 https://bankauctiondeals.com/
 tell me more </t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>u/NewtImportant3670</t>
         </is>
       </c>
-      <c r="P11" s="2" t="n">
+      <c r="P10" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q11" s="2" t="n">
+      <c r="Q10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R11" s="2" t="n">
+      <c r="R10" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="S11" s="3" t="inlineStr">
+      <c r="S10" s="3" t="inlineStr">
         <is>
           <t>https://reddit.com/r/hyderabadrealestate/comments/1t797wy/i_need_trusted_websites_to_search_for_bank/</t>
         </is>
       </c>
-      <c r="T11" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T11"/>
+  <autoFilter ref="A1:T10"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S3" r:id="rId2"/>
@@ -1437,7 +1355,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S8" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S9" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S10" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S11" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1449,7 +1366,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1535,7 +1452,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -1581,7 +1498,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -1612,7 +1529,7 @@
         <v>2</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>100</v>
@@ -1631,7 +1548,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -1664,7 +1581,7 @@
         <v>2</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>100</v>
@@ -1683,7 +1600,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>8.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -1729,7 +1646,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -1775,7 +1692,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>10.6</v>
+        <v>11.4</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -1817,7 +1734,7 @@
         <v>2</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>100</v>
@@ -1840,7 +1757,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>10.9</v>
+        <v>11.7</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -1909,7 +1826,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>13.3</v>
+        <v>14.1</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -1946,10 +1863,10 @@
         <v>0</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
@@ -1965,7 +1882,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>13.9</v>
+        <v>14.7</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -2006,13 +1923,13 @@
         </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I10" s="2" t="n">
         <v>4</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
@@ -2032,7 +1949,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>14.3</v>
+        <v>15.1</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
@@ -2078,7 +1995,7 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>15.5</v>
+        <v>16.3</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
@@ -2125,7 +2042,7 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>23</v>
+        <v>23.8</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
@@ -2164,54 +2081,8 @@
       </c>
       <c r="L13" s="2" t="inlineStr"/>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-08 01:16</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>hyderabadrealestate</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr"/>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Jayabheri Nirvana</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Buying a flat in jayabheri nirvana. Give me the pros and cons please. The major con I think of is the traffic near the market.</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>u/stoopidpotato_</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J14" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>https://reddit.com/r/hyderabadrealestate/comments/1t6laei/jayabheri_nirvana/</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:L14"/>
+  <autoFilter ref="A1:L13"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -2227,7 +2098,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2325,7 +2195,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>5.7</v>
+        <v>6.5</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -2357,7 +2227,7 @@
 ————————
 We’re in education and this property is on the name of our educational Trust.
 We’ve sold several other properties of ours without issue until now. But with this one, I’ve been facing some trouble.
-I’ve had deals with 3 buyers in the last 5 months, who were willing to pay a good amount, fall apart after their advocates said that as it is a high value deal, it is better for us to get a court permission to sell this property. This process will take 6-12 months, which is longer than I’m willing to wait.
+I’ve had deals with 3 buyers in the last few months, who were willing to pay a good amount, fall apart after their advocates said that as it is a high value deal, it is better for us to get a court permission to sell this property. This process will take 6-12 months, which is longer than I’m willing to wait.
 Our other properties were under 2 Cr, but nobody ever asked for this court permission before though they all also got legal opinions prior to purchasing.
 So can anyone please give alternative solutions? Or please let me know if anybody is looking to invest in east Hyderabad.</t>
         </is>
@@ -2368,13 +2238,13 @@
         </is>
       </c>
       <c r="H2" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
@@ -2394,7 +2264,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>8.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -2440,7 +2310,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>10.6</v>
+        <v>11.4</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -2482,7 +2352,7 @@
         <v>2</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>100</v>
@@ -2505,7 +2375,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>10.9</v>
+        <v>11.7</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -2574,7 +2444,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>11</v>
+        <v>11.8</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -2611,7 +2481,7 @@
         <v>20</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
@@ -2627,7 +2497,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>13.3</v>
+        <v>14.1</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -2664,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
@@ -2683,7 +2553,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>14.3</v>
+        <v>15.1</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -2729,7 +2599,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>15.1</v>
+        <v>15.9</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -2881,7 +2751,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -2927,7 +2797,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -2958,7 +2828,7 @@
         <v>2</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>100</v>
@@ -2977,7 +2847,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -3031,7 +2901,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -3081,7 +2951,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>5.7</v>
+        <v>6.5</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -3113,7 +2983,7 @@
 ————————
 We’re in education and this property is on the name of our educational Trust.
 We’ve sold several other properties of ours without issue until now. But with this one, I’ve been facing some trouble.
-I’ve had deals with 3 buyers in the last 5 months, who were willing to pay a good amount, fall apart after their advocates said that as it is a high value deal, it is better for us to get a court permission to sell this property. This process will take 6-12 months, which is longer than I’m willing to wait.
+I’ve had deals with 3 buyers in the last few months, who were willing to pay a good amount, fall apart after their advocates said that as it is a high value deal, it is better for us to get a court permission to sell this property. This process will take 6-12 months, which is longer than I’m willing to wait.
 Our other properties were under 2 Cr, but nobody ever asked for this court permission before though they all also got legal opinions prior to purchasing.
 So can anyone please give alternative solutions? Or please let me know if anybody is looking to invest in east Hyderabad.</t>
         </is>
@@ -3124,13 +2994,13 @@
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
@@ -3150,7 +3020,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -3197,7 +3067,7 @@
         <v>4</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>83</v>
@@ -3216,7 +3086,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>10.6</v>
+        <v>11.4</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -3258,7 +3128,7 @@
         <v>2</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>100</v>
@@ -3281,7 +3151,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>10.9</v>
+        <v>11.7</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -3350,7 +3220,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>13.3</v>
+        <v>14.1</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -3387,10 +3257,10 @@
         <v>0</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
@@ -3511,7 +3381,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -3557,7 +3427,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -3605,7 +3475,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>11</v>
+        <v>11.8</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -3651,7 +3521,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>11.2</v>
+        <v>12</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -3680,7 +3550,7 @@
         </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I5" s="2" t="n">
         <v>6</v>
@@ -3706,7 +3576,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>19.9</v>
+        <v>20.7</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -3747,13 +3617,13 @@
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>11</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
@@ -3783,7 +3653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S11"/>
+  <dimension ref="A1:S10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3952,13 +3822,13 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Diverse activity dominated by H1B/immigration topics with a single genuine inquiry about buying property in Hyderabad.</t>
+          <t>Diverse activity centered on H1B/immigration with a single genuine inquiry about buying property in Hyderabad.</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr"/>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Only 5.9% activity in real estate subs | High subreddit diversity (H1B, immigration, NYC) | No promotional language | Post asks for plots/flats rather than pitching | Conversational personal-context comments</t>
+          <t>Only 5.9% RE activity, mostly H1B/immigration subs | Post asks for plots/flats rather than pitching | No promotional language or contact info | Conversational personal-context comments</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -4025,13 +3895,13 @@
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Diverse activity across hobbies, gadgets, and personal finance with genuine question-asking tone about a personal property purchase.</t>
+          <t>Diverse subreddit activity and personal-context questions about buying property indicate a genuine buyer researching purchase decisions.</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr"/>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>High subreddit diversity (7) including iPad, perfume, EV subs | Posts ask questions with personal context (loan amount, specific location) | No promotional language hits | Conversational comments seeking advice rather than offering services</t>
+          <t>Diverse interests: iPad, iPhone, perfumes, EVs, personal finance | Asks investment questions rather than pitching | No promotional language | Conversational tone with follow-up questions</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -4104,7 +3974,7 @@
       <c r="O4" s="2" t="inlineStr"/>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>No real estate activity | No promotional language | Single casual comment in local subreddit</t>
+          <t>Only 1 comment in 90 days | No real estate activity | No promotional language | Comment is personal/conversational in Telugu</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr"/>
@@ -4131,7 +4001,7 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>1348</v>
@@ -4167,13 +4037,13 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Personal narrative about own housing decisions with family context, no promotional language or agent behavior.</t>
+          <t>Personal narrative about own housing decisions with family context, no promotional language or sales pitch.</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr"/>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Personal first-person story about buying vs renting | Mentions husband and life plans | No promotional language or service offers | No recent posting activity in RE subs</t>
+          <t>Personal first-person story about renting vs buying | Mentions husband and relocation plans | No promotional language or contact solicitation | No recent posting activity in RE subs</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr"/>
@@ -4236,13 +4106,13 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>No real estate activity at all; comments span news/politics and tech topics indicating a regular Reddit user.</t>
+          <t>No real estate activity at all; comments span news, religion debates, and tech bugs, indicating a regular user.</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr"/>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>0% real estate activity in last 90 days | No promotional language | Comments on diverse topics (geopolitics, iOS bugs) | Old account with modest karma</t>
+          <t>0% real estate activity in last 90 days | No promotional language | Diverse comment topics (news, tech, politics) | Old account with conversational tone</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr"/>
@@ -4305,13 +4175,13 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>No recent activity or content available to classify the user.</t>
+          <t>No recent activity or content available to evaluate.</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr"/>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>No posts or comments in last 90 days | Zero promo language hits</t>
+          <t>account exists but inactive in last 90 days</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr"/>
@@ -4370,13 +4240,13 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Diverse non-real-estate activity with no promotional real estate content suggests a regular Redditor.</t>
+          <t>Diverse non-real-estate activity with no real estate posts or promotional property pitches.</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr"/>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>0% real estate activity in last 90 days | Active in mubi, creditcards, askindianwomen - diverse interests | No promotional language hits | Conversational tone in comments</t>
+          <t>0% real estate activity in 90 days | Diverse subs: mubi, thirtiesindia, creditcardsindia, askindianwomen | Conversational personal comments | No promotional language hits</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr"/>
@@ -4440,17 +4310,17 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Repeated specific personal buying queries for one flat configuration in one project, with conversational comments showing buyer perspective rather than sales pitches.</t>
+          <t>Repeated specific posts seeking to buy one particular flat configuration with personal preferences, and comments reflect a buyer's perspective rather than sales pitches.</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>High RE concentration (64%) | Repetitive post titles could look spammy</t>
+          <t>High concentration in real estate subs (64%) | Repetitive posts could look spammy</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>Posts ask to buy, not sell | Very specific personal requirement (2160 sft, J block) | Comments express buyer caution about builders and loans | No DM/contact/promo pitches | Low karma, small account - not a professional presence</t>
+          <t>Posts ask to buy, not sell | Personal preferences (higher floors, newer blocks) | Comments warn against builders and home loans - buyer mindset | No DM/contact/promotional pitches | Low karma, small account - not a professional poster</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4523,7 +4393,7 @@
       <c r="O10" s="2" t="inlineStr"/>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>account_age 1707 days but zero recent posts/comments | no subreddit activity to analyze</t>
+          <t>No posts or comments in last 90 days | Very low total karma | No subreddit activity to analyze</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr"/>
@@ -4534,78 +4404,8 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>u/stoopidpotato_</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>end_user</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>2002</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>1335</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>408</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>927</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>celebs_hotness(1)</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>Zero real estate activity and diverse personal/civic comments indicate a regular Reddit user, not an agent.</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr"/>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>0% real estate activity in last 90 days | No promotional language | Personal, conversational tone across varied topics | Asks personal questions (mom's voter ID)</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr"/>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>GO AWAY YOU DISGUSTING PEOPLE, SHE WAS BEING RAPED STOP JERKING TO THIS!!!!!!!!!!!! | Haan zaroor aur Diwali ke time pollution delhi me bohot sari gadi chalane ki vajah se itna zyada bad | hey,
-this is the landline number for secretary of higher education, Shri Sanjay Murthy. Please call  | Can my mom just bring her old voter id and aadhar? We can't find her voting slip online.</t>
-        </is>
-      </c>
-      <c r="S11" s="3" t="inlineStr">
-        <is>
-          <t>https://reddit.com/user/stoopidpotato_</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:S11"/>
+  <autoFilter ref="A1:S10"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S3" r:id="rId2"/>
@@ -4616,7 +4416,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
